--- a/fixtures/sparse500.xlsx
+++ b/fixtures/sparse500.xlsx
@@ -9,25 +9,50 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="1">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
